--- a/Luban/Config/Datas/#WeatherPoolConfig.xlsx
+++ b/Luban/Config/Datas/#WeatherPoolConfig.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7957CBA-CF34-49E2-8FCB-2EBC200BA067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B98418E-6406-4E86-9C0F-BB8816AD6AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6315" yWindow="3930" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -452,12 +452,6 @@
       <c r="C3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B4" s="2">
@@ -466,8 +460,12 @@
       <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
+      <c r="D4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B5" s="2"/>

--- a/Luban/Config/Datas/#WeatherPoolConfig.xlsx
+++ b/Luban/Config/Datas/#WeatherPoolConfig.xlsx
@@ -1,24 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project\Return0\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B98418E-6406-4E86-9C0F-BB8816AD6AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDEBEB30-CB92-4CA9-814F-D8B4E6B46F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6315" yWindow="3930" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2835" yWindow="4290" windowWidth="35565" windowHeight="9315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
